--- a/semesters/25-26-2/OTK-AAI2EG-INF22/runtime.xlsx
+++ b/semesters/25-26-2/OTK-AAI2EG-INF22/runtime.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositories\elte-otk-jegyzetek\semesters\25-26-2\OTK-AAI2EG-INF22\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{148AF276-CF23-4974-8907-6B87A8245873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C122B10-A63D-449A-88E4-0B0B4157C1C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{796946CD-12B1-47A3-8724-DA3068045590}"/>
+    <workbookView xWindow="11190" yWindow="0" windowWidth="11460" windowHeight="14410" xr2:uid="{796946CD-12B1-47A3-8724-DA3068045590}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -540,7 +540,7 @@
   <dimension ref="A1:J152"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.453125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="27" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.36328125" style="1" customWidth="1"/>
     <col min="3" max="3" width="15.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="10" width="15.54296875" style="1" customWidth="1"/>
